--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337794</v>
+        <v>130337787</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688817</v>
+        <v>688944</v>
       </c>
       <c r="R2" t="n">
-        <v>6631495</v>
+        <v>6631442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337787</v>
+        <v>130337794</v>
       </c>
       <c r="B3" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688944</v>
+        <v>688817</v>
       </c>
       <c r="R3" t="n">
-        <v>6631442</v>
+        <v>6631495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337794</v>
+        <v>130337787</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>101112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688817</v>
+        <v>688944</v>
       </c>
       <c r="R2" t="n">
-        <v>6631495</v>
+        <v>6631442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337787</v>
+        <v>130337794</v>
       </c>
       <c r="B3" t="n">
-        <v>101109</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688944</v>
+        <v>688817</v>
       </c>
       <c r="R3" t="n">
-        <v>6631442</v>
+        <v>6631495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>92146</v>
+        <v>92149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98954</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337787</v>
+        <v>130337794</v>
       </c>
       <c r="B2" t="n">
-        <v>101112</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688944</v>
+        <v>688817</v>
       </c>
       <c r="R2" t="n">
-        <v>6631442</v>
+        <v>6631495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337794</v>
+        <v>130337791</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688817</v>
+        <v>688923</v>
       </c>
       <c r="R3" t="n">
-        <v>6631495</v>
+        <v>6631393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>101138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R4" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>92149</v>
+        <v>92175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>98983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96269</v>
+        <v>96295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130337796</v>
       </c>
       <c r="B13" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1225,54 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>92176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R7" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,57 +1320,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B8" t="n">
-        <v>92175</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R8" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98983</v>
+        <v>98984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1225,45 +1225,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>92176</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R7" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,66 +1334,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R8" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98984</v>
+        <v>98985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96296</v>
+        <v>96297</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130337794</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>101142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R3" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B4" t="n">
-        <v>101140</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R4" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98985</v>
+        <v>98987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130337796</v>
       </c>
       <c r="B13" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -787,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B3" t="n">
-        <v>101142</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R3" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>101146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R4" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1225,54 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>92179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R7" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,57 +1320,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B8" t="n">
-        <v>92179</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R8" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98987</v>
+        <v>98991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96299</v>
+        <v>96303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337794</v>
+        <v>130337787</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>101146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688817</v>
+        <v>688944</v>
       </c>
       <c r="R2" t="n">
-        <v>6631495</v>
+        <v>6631442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337791</v>
+        <v>130337794</v>
       </c>
       <c r="B3" t="n">
         <v>57851</v>
@@ -823,14 +818,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688923</v>
+        <v>688817</v>
       </c>
       <c r="R3" t="n">
-        <v>6631393</v>
+        <v>6631495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B4" t="n">
-        <v>101146</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R4" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130337787</v>
       </c>
       <c r="B2" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130337794</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130337791</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130337784</v>
       </c>
       <c r="B7" t="n">
-        <v>92179</v>
+        <v>92192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>130333209</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>98991</v>
+        <v>99004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96303</v>
+        <v>96316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130337796</v>
       </c>
       <c r="B13" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337787</v>
+        <v>130337794</v>
       </c>
       <c r="B2" t="n">
-        <v>101159</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688944</v>
+        <v>688817</v>
       </c>
       <c r="R2" t="n">
-        <v>6631442</v>
+        <v>6631495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337794</v>
+        <v>130337791</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688817</v>
+        <v>688923</v>
       </c>
       <c r="R3" t="n">
-        <v>6631495</v>
+        <v>6631393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>101160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R4" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,45 +1225,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>92192</v>
+        <v>98971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R7" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,66 +1334,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>98970</v>
+        <v>92193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R8" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>99004</v>
+        <v>99005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96316</v>
+        <v>96317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130337796</v>
       </c>
       <c r="B13" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130337794</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>101163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R3" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B4" t="n">
-        <v>101160</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R4" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>130337785</v>
       </c>
       <c r="B5" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,54 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B7" t="n">
-        <v>98971</v>
+        <v>92194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R7" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,57 +1320,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B8" t="n">
-        <v>92193</v>
+        <v>98974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R8" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>130337792</v>
       </c>
       <c r="B9" t="n">
-        <v>99005</v>
+        <v>99008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>130337789</v>
       </c>
       <c r="B10" t="n">
-        <v>96317</v>
+        <v>96320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130337788</v>
       </c>
       <c r="B11" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130337798</v>
       </c>
       <c r="B12" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>130337796</v>
       </c>
       <c r="B13" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -787,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B3" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R3" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>101163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R4" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1225,45 +1225,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B7" t="n">
-        <v>92194</v>
+        <v>98974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R7" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,66 +1334,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B8" t="n">
-        <v>98974</v>
+        <v>92194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R8" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337794</v>
+        <v>130337791</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -711,14 +711,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688817</v>
+        <v>688923</v>
       </c>
       <c r="R2" t="n">
-        <v>6631495</v>
+        <v>6631393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337791</v>
+        <v>130337794</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -823,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688923</v>
+        <v>688817</v>
       </c>
       <c r="R3" t="n">
-        <v>6631393</v>
+        <v>6631495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337791</v>
+        <v>130337787</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>101163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688923</v>
+        <v>688944</v>
       </c>
       <c r="R2" t="n">
-        <v>6631393</v>
+        <v>6631442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337787</v>
+        <v>130337791</v>
       </c>
       <c r="B4" t="n">
-        <v>101163</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688944</v>
+        <v>688923</v>
       </c>
       <c r="R4" t="n">
-        <v>6631442</v>
+        <v>6631393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1225,54 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130333209</v>
+        <v>130337784</v>
       </c>
       <c r="B7" t="n">
-        <v>98974</v>
+        <v>92194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688732</v>
+        <v>688971</v>
       </c>
       <c r="R7" t="n">
-        <v>6631536</v>
+        <v>6631478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,57 +1320,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130337784</v>
+        <v>130333209</v>
       </c>
       <c r="B8" t="n">
-        <v>92194</v>
+        <v>98974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688971</v>
+        <v>688732</v>
       </c>
       <c r="R8" t="n">
-        <v>6631478</v>
+        <v>6631536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,12 +1441,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130337787</v>
+        <v>130337788</v>
       </c>
       <c r="B2" t="n">
-        <v>101163</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688944</v>
+        <v>688986</v>
       </c>
       <c r="R2" t="n">
-        <v>6631442</v>
+        <v>6631418</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130337794</v>
+        <v>130337782</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688817</v>
+        <v>689054</v>
       </c>
       <c r="R3" t="n">
-        <v>6631495</v>
+        <v>6631389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130337791</v>
+        <v>130337789</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688923</v>
+        <v>688988</v>
       </c>
       <c r="R4" t="n">
-        <v>6631393</v>
+        <v>6631416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130337785</v>
+        <v>130337777</v>
       </c>
       <c r="B5" t="n">
-        <v>101163</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688911</v>
+        <v>688811</v>
       </c>
       <c r="R5" t="n">
-        <v>6631505</v>
+        <v>6631662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,11 +1111,11 @@
         <v>130337790</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1225,45 +1220,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130337784</v>
+        <v>130337791</v>
       </c>
       <c r="B7" t="n">
-        <v>92194</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040162</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Orrängarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688971</v>
+        <v>688923</v>
       </c>
       <c r="R7" t="n">
-        <v>6631478</v>
+        <v>6631393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,54 +1332,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130333209</v>
+        <v>130337794</v>
       </c>
       <c r="B8" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jättetallen, Jättetallen, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688732</v>
+        <v>688817</v>
       </c>
       <c r="R8" t="n">
-        <v>6631536</v>
+        <v>6631495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Svårt att räkna, delvis snötäckt.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130337792</v>
+        <v>130337795</v>
       </c>
       <c r="B9" t="n">
-        <v>99008</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,34 +1455,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>688833</v>
+        <v>688790</v>
       </c>
       <c r="R9" t="n">
-        <v>6631489</v>
+        <v>6631464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130337789</v>
+        <v>130337799</v>
       </c>
       <c r="B10" t="n">
-        <v>96320</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1567,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688988</v>
+        <v>688567</v>
       </c>
       <c r="R10" t="n">
-        <v>6631416</v>
+        <v>6631386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,45 +1668,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130337788</v>
+        <v>130337796</v>
       </c>
       <c r="B11" t="n">
-        <v>97220</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Orrängarna, Upl</t>
+          <t>Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>688986</v>
+        <v>688681</v>
       </c>
       <c r="R11" t="n">
-        <v>6631418</v>
+        <v>6631459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130337798</v>
+        <v>130337792</v>
       </c>
       <c r="B12" t="n">
-        <v>101163</v>
+        <v>99153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>688659</v>
+        <v>688833</v>
       </c>
       <c r="R12" t="n">
-        <v>6631438</v>
+        <v>6631489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,45 +1882,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130337796</v>
+        <v>130333209</v>
       </c>
       <c r="B13" t="n">
-        <v>58236</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jättetallen, Upl</t>
+          <t>Jättetallen, Jättetallen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688681</v>
+        <v>688732</v>
       </c>
       <c r="R13" t="n">
-        <v>6631459</v>
+        <v>6631536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Svårt att räkna, delvis snötäckt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,15 +1991,657 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130337780</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Orrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>689026</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6631318</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130337783</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Orrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>689039</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6631392</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130337785</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Orrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>688911</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6631505</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130337787</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Orrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>688944</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6631442</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130337798</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jättetallen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>688659</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6631438</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130337784</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Orrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>688971</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6631478</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61099-2025 artfynd.xlsx
+++ b/artfynd/A 61099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337790</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337791</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337794</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337795</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337799</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337796</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337792</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333209</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337780</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2214,6 +2284,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337783</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337785</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337787</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2535,6 +2620,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337798</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,8 +2732,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130337784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>